--- a/audits/lubriderm/lubriderm_audit.xlsx
+++ b/audits/lubriderm/lubriderm_audit.xlsx
@@ -516,21 +516,21 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] / Disodium EDTA [inferred: -EDTA] [4]</t>
+          <t>Mineral Oil [1] / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magnesium Aspartate, Zinc Gluconate, Copper Gluconate</t>
+          <t>unknown — manual review needed: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s): Mineral Oil, Carbomer, Phenoxyethanol, Fragrance. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted.</t>
+          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] / Disodium EDTA [inferred: -EDTA] [4]</t>
+          <t>Mineral Oil [1] / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magnesium Aspartate, Zinc Gluconate, Copper Gluconate</t>
+          <t>unknown — manual review needed: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s): Mineral Oil, Carbomer, Phenoxyethanol, Fragrance. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package.</t>
+          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Polysorbate 60 [PDF] [1,2,4,5] / Ceteareth-20 [inferred: -eth ethoxylate] [1,4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Sodium Hydroxide</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>PFAS, carcinogen in leave-on</t>
@@ -668,13 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s): Mineral Oil, Dimethicone, Carbomer, Polysorbate 60 [PDF]. Escalation: PFAS, carcinogen in leave-on.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Sodium Hydroxide.</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -706,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -714,29 +722,29 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cocamidopropyl Betaine [1,4] / PEG-80 Sorbitan Laurate [inferred: PEG-] [1,2,4,5] / Sodium Cocoyl Isethionate [1]</t>
+          <t>Cocamidopropyl Betaine [1,4] / PEG-80 Sorbitan Laurate [1,2,4,5] (inferred: PEG-) / Sodium Cocoyl Isethionate [1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Tocopheryl Acetate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Cocamidopropyl Betaine, PEG-80 Sorbitan Laurate, Sodium Cocoyl Isethionate.</t>
+          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate).</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -768,21 +776,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Polysorbate 60 [PDF] [1,2,4,5] / Ceteareth-20 [inferred: -eth ethoxylate] [1,4,5] / Disodium EDTA [inferred: -EDTA] [4] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Zinc Gluconate, Copper Gluconate, Magnesium Aspartate</t>
+          <t>unknown — manual review needed: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Disodium EDTA, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -792,17 +800,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s): Mineral Oil, Dimethicone, Carbomer, Polysorbate 60 [PDF]. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy.</t>
+          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Disodium EDTA, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avoid (Moderate)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -842,29 +850,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cocamidopropyl Betaine [1,4] / PEG-80 Sorbitan Laurate [inferred: PEG-] [1,2,4,5] / Sodium Cocoyl Isethionate [1] / Glycol Distearate [4] / Fragrance [1,2,4,8]</t>
+          <t>Cocamidopropyl Betaine [1,4] / PEG-80 Sorbitan Laurate [1,2,4,5] (inferred: PEG-) / Sodium Cocoyl Isethionate [1] / Glycol Distearate [4] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s): Cocamidopropyl Betaine, PEG-80 Sorbitan Laurate, Sodium Cocoyl Isethionate, Glycol Distearate.</t>
+          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list.</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -890,7 +898,11 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -900,12 +912,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Not graded: no verbatim ingredient list on the product page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bundle page has no printed INCI list in its visible text. The page's CMS holds a function-grouped ingredient explanation (e.g. 'Carbomer, Palmitic Acid; Stearic Acid ...', 'Titanium Dioxide', 'Citric Acid, Sodium Citrate, Sodium Hydroxide', 'Caprylyl Glycol', 'Phenoxyethanol') that is not a verbatim ingredient list and is not used for grading. Not graded. Manual check of the package is needed.</t>
+          <t>Bundle page has no printed INCI list in its visible text. The page's CMS holds a function-grouped ingredient explanation (e.g. 'Carbomer, Palmitic Acid; Stearic Acid ...', 'Titanium Dioxide', 'Citric Acid, Sodium Citrate, Sodium Hydroxide', 'Caprylyl Glycol', 'Phenoxyethanol') that is not a verbatim ingredient list and is not used for grading. Not graded. Manual check of the package is needed. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">

--- a/audits/lubriderm/lubriderm_audit.xlsx
+++ b/audits/lubriderm/lubriderm_audit.xlsx
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
+          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
+          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Sodium Hydroxide.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -734,12 +734,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3.</t>
+          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Tocopheryl Acetate.</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Disodium EDTA, Sodium Hydroxide.</t>
+          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Disodium EDTA, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -862,12 +862,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter.</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">

--- a/audits/lubriderm/lubriderm_audit.xlsx
+++ b/audits/lubriderm/lubriderm_audit.xlsx
@@ -652,17 +652,17 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8]</t>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Polysorbate 60 [1,2,4,5] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Lecithin, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Sodium Hydroxide.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Lecithin, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -780,17 +780,17 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / Carbomer [1,4,6] / Polysorbate 60 [1,2,4,5] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Disodium EDTA, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Lecithin, Disodium EDTA, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Polysorbate 60, Lecithin, Disodium EDTA, Sodium Hydroxide.</t>
+          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Lecithin, Disodium EDTA, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">

--- a/audits/lubriderm/lubriderm_audit.xlsx
+++ b/audits/lubriderm/lubriderm_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Carbomer, Phenoxyethanol); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
+          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -606,17 +606,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Carbomer, Phenoxyethanol); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Potassium Cetyl Phosphate, Sodium Polyacrylate, Hydrogenated Palm Glycerides, Sodium Hydroxide, Butyrospermum Parkii (Shea) Butter, Disodium EDTA, Avena Sativa (Oat) Kernel Oil, Magnesium Aspartate, Zinc Gluconate, Copper Gluconate.</t>
+          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, Carbomer); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Palmitic Acid, Stearic Acid, Lecithin, Sodium Hydroxide.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Mild)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -734,17 +734,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3.</t>
+          <t>3 flagged ingredient(s) in the printed list (Cocamidopropyl Betaine, PEG-80 Sorbitan Laurate, Sodium Cocoyl Isethionate); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Tocopheryl Acetate.</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -800,17 +800,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, Carbomer); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sorbitol, Caprylic/Capric Triglyceride, Tocopheryl Acetate, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter, Zinc Gluconate, Copper Gluconate, Magnesium Aspartate, Palmitic Acid, Stearic Acid, Lecithin, Disodium EDTA, Sodium Hydroxide.</t>
+          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -862,17 +862,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>5 flagged ingredient(s) in the printed list (Cocamidopropyl Betaine, PEG-80 Sorbitan Laurate, Sodium Cocoyl Isethionate); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Avena Sativa (Oat) Kernel Flour, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Caprylic/Capric Triglyceride, Avena Sativa (Oat) Kernel Oil, Butyrospermum Parkii (Shea) Butter.</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bundle page has no printed INCI list in its visible text. The page's CMS holds a function-grouped ingredient explanation (e.g. 'Carbomer, Palmitic Acid; Stearic Acid ...', 'Titanium Dioxide', 'Citric Acid, Sodium Citrate, Sodium Hydroxide', 'Caprylyl Glycol', 'Phenoxyethanol') that is not a verbatim ingredient list and is not used for grading. Not graded. Manual check of the package is needed. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>Bundle page has no printed INCI list in its visible text. The page's CMS holds a function-grouped ingredient explanation (e.g. 'Carbomer, Palmitic Acid; Stearic Acid ...', 'Titanium Dioxide', 'Citric Acid, Sodium Citrate, Sodium Hydroxide', 'Caprylyl Glycol', 'Phenoxyethanol') that is not a verbatim ingredient list and is not used for grading. Not graded. Manual check of the package is needed. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">

--- a/audits/lubriderm/lubriderm_audit.xlsx
+++ b/audits/lubriderm/lubriderm_audit.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Product copy says 'Free of parabens, phthalates, dyes, and fragrance' but the printed ingredient list includes 'Fragrance'. Conflict noted. Identical printed text on 1 other product(s): Daily Moisture Lotion. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Printed ingredient list is character-identical to Daily Moisture Lotion Fragrance-Free (which says it is fragrance-free). This product's copy claims only 'Free of parabens, phthalates, and dyes', so the identical list (including 'Fragrance') may be a page data error. Needs manual verification against the product package. Identical printed text on 1 other product(s): Daily Moisture Lotion Fragrance-Free. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates'. No sulfate-named ingredient in the printed list; 'Sodium Cocoyl Isethionate' is an isethionate (not a sulfate). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Product copy says 'Hypoallergenic and lightly scented'; printed list includes 'Fragrance'. Consistent with copy. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Product copy says 'Free of Parabens, Phthalates, Dyes, Sulfates' and 'Lightly scented'; printed list includes 'Fragrance'. Consistent with 'lightly scented' copy. No sulfate-named ingredient in the list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
